--- a/data/sars/atlantic/tables/Atlantic_2009_Table1.xlsx
+++ b/data/sars/atlantic/tables/Atlantic_2009_Table1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/atlantic/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3E0A27-5B4A-B24F-A2AA-848D8BBCF9E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3B3848-9FC7-0C42-A006-DDA8F97D36F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="500" windowWidth="34480" windowHeight="20820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="101">
   <si>
     <t>North Atlantic right whale</t>
   </si>
@@ -107,9 +107,6 @@
   </si>
   <si>
     <t>Blainville‘s beaked whale</t>
-  </si>
-  <si>
-    <t>Y (new report)</t>
   </si>
   <si>
     <t>Gervais beaked whale</t>
@@ -337,6 +334,9 @@
   </si>
   <si>
     <t>msi_fisheries_cv</t>
+  </si>
+  <si>
+    <t>new report</t>
   </si>
 </sst>
 </file>
@@ -786,49 +786,49 @@
   <sheetData>
     <row r="1" spans="1:19" ht="30" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="L1" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="O1" s="4" t="s">
         <v>81</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>82</v>
       </c>
       <c r="P1" s="5"/>
       <c r="Q1" s="5"/>
@@ -876,7 +876,7 @@
         <v>3</v>
       </c>
       <c r="O2" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P2" s="8"/>
       <c r="Q2" s="8"/>
@@ -924,7 +924,7 @@
         <v>3</v>
       </c>
       <c r="O3" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P3" s="8"/>
       <c r="Q3" s="8"/>
@@ -972,7 +972,7 @@
         <v>3</v>
       </c>
       <c r="O4" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P4" s="8"/>
       <c r="Q4" s="8"/>
@@ -1020,7 +1020,7 @@
         <v>3</v>
       </c>
       <c r="O5" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P5" s="8"/>
       <c r="Q5" s="8"/>
@@ -1068,7 +1068,7 @@
         <v>3</v>
       </c>
       <c r="O6" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P6" s="8"/>
       <c r="Q6" s="8"/>
@@ -1481,9 +1481,11 @@
         <v>11</v>
       </c>
       <c r="N15" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O15" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="O15" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="P15" s="10"/>
       <c r="Q15" s="10"/>
       <c r="R15" s="10"/>
@@ -1491,7 +1493,7 @@
     </row>
     <row r="16" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A16" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>1</v>
@@ -1528,9 +1530,11 @@
         <v>11</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O16" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="O16" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="P16" s="10"/>
       <c r="Q16" s="10"/>
       <c r="R16" s="10"/>
@@ -1538,7 +1542,7 @@
     </row>
     <row r="17" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A17" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>1</v>
@@ -1575,9 +1579,11 @@
         <v>11</v>
       </c>
       <c r="N17" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O17" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="O17" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="P17" s="10"/>
       <c r="Q17" s="10"/>
       <c r="R17" s="10"/>
@@ -1585,7 +1591,7 @@
     </row>
     <row r="18" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A18" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>1</v>
@@ -1622,9 +1628,11 @@
         <v>11</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O18" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="P18" s="10"/>
       <c r="Q18" s="10"/>
       <c r="R18" s="10"/>
@@ -1632,7 +1640,7 @@
     </row>
     <row r="19" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A19" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>1</v>
@@ -1679,7 +1687,7 @@
     </row>
     <row r="20" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A20" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>1</v>
@@ -1721,7 +1729,7 @@
         <v>3</v>
       </c>
       <c r="O20" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P20" s="10"/>
       <c r="Q20" s="10"/>
@@ -1730,7 +1738,7 @@
     </row>
     <row r="21" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A21" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>1</v>
@@ -1772,7 +1780,7 @@
         <v>3</v>
       </c>
       <c r="O21" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P21" s="10"/>
       <c r="Q21" s="10"/>
@@ -1781,7 +1789,7 @@
     </row>
     <row r="22" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A22" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>1</v>
@@ -1823,7 +1831,7 @@
         <v>3</v>
       </c>
       <c r="O22" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P22" s="10"/>
       <c r="Q22" s="10"/>
@@ -1832,7 +1840,7 @@
     </row>
     <row r="23" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A23" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>1</v>
@@ -1874,7 +1882,7 @@
         <v>3</v>
       </c>
       <c r="O23" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P23" s="10"/>
       <c r="Q23" s="10"/>
@@ -1883,7 +1891,7 @@
     </row>
     <row r="24" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A24" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>1</v>
@@ -1930,7 +1938,7 @@
     </row>
     <row r="25" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A25" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>1</v>
@@ -1972,7 +1980,7 @@
         <v>3</v>
       </c>
       <c r="O25" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P25" s="10"/>
       <c r="Q25" s="10"/>
@@ -1981,7 +1989,7 @@
     </row>
     <row r="26" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A26" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>1</v>
@@ -2030,7 +2038,7 @@
     </row>
     <row r="27" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A27" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>1</v>
@@ -2079,7 +2087,7 @@
     </row>
     <row r="28" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A28" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>1</v>
@@ -2126,7 +2134,7 @@
     </row>
     <row r="29" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A29" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>1</v>
@@ -2173,7 +2181,7 @@
     </row>
     <row r="30" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A30" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>1</v>
@@ -2220,7 +2228,7 @@
     </row>
     <row r="31" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A31" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>1</v>
@@ -2244,7 +2252,7 @@
         <v>0.5</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J31" s="12">
         <v>0</v>
@@ -2267,7 +2275,7 @@
     </row>
     <row r="32" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A32" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>1</v>
@@ -2314,10 +2322,10 @@
     </row>
     <row r="33" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A33" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>47</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>48</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>18</v>
@@ -2354,7 +2362,7 @@
         <v>25</v>
       </c>
       <c r="O33" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P33" s="10"/>
       <c r="Q33" s="10"/>
@@ -2363,10 +2371,10 @@
     </row>
     <row r="34" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A34" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>18</v>
@@ -2410,10 +2418,10 @@
     </row>
     <row r="35" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A35" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>18</v>
@@ -2434,7 +2442,7 @@
         <v>0.5</v>
       </c>
       <c r="I35" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J35" s="6" t="s">
         <v>13</v>
@@ -2447,9 +2455,11 @@
         <v>3</v>
       </c>
       <c r="N35" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O35" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="O35" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="P35" s="10"/>
       <c r="Q35" s="10"/>
       <c r="R35" s="10"/>
@@ -2457,10 +2467,10 @@
     </row>
     <row r="36" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A36" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>18</v>
@@ -2481,7 +2491,7 @@
         <v>0.5</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J36" s="6" t="s">
         <v>13</v>
@@ -2494,9 +2504,11 @@
         <v>3</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O36" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="O36" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="P36" s="10"/>
       <c r="Q36" s="10"/>
       <c r="R36" s="10"/>
@@ -2504,10 +2516,10 @@
     </row>
     <row r="37" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A37" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>18</v>
@@ -2541,9 +2553,11 @@
         <v>3</v>
       </c>
       <c r="N37" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O37" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="O37" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="P37" s="10"/>
       <c r="Q37" s="10"/>
       <c r="R37" s="10"/>
@@ -2551,10 +2565,10 @@
     </row>
     <row r="38" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A38" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>18</v>
@@ -2588,9 +2602,11 @@
         <v>3</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O38" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="O38" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="P38" s="10"/>
       <c r="Q38" s="10"/>
       <c r="R38" s="10"/>
@@ -2598,10 +2614,10 @@
     </row>
     <row r="39" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A39" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>18</v>
@@ -2635,9 +2651,11 @@
         <v>3</v>
       </c>
       <c r="N39" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O39" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="O39" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="P39" s="10"/>
       <c r="Q39" s="10"/>
       <c r="R39" s="10"/>
@@ -2645,10 +2663,10 @@
     </row>
     <row r="40" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A40" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>18</v>
@@ -2682,9 +2700,11 @@
         <v>3</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O40" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="O40" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="P40" s="10"/>
       <c r="Q40" s="10"/>
       <c r="R40" s="10"/>
@@ -2692,10 +2712,10 @@
     </row>
     <row r="41" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A41" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>18</v>
@@ -2729,9 +2749,11 @@
         <v>3</v>
       </c>
       <c r="N41" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O41" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="O41" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="P41" s="10"/>
       <c r="Q41" s="10"/>
       <c r="R41" s="10"/>
@@ -2739,10 +2761,10 @@
     </row>
     <row r="42" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A42" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>18</v>
@@ -2776,9 +2798,11 @@
         <v>3</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O42" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="O42" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="P42" s="10"/>
       <c r="Q42" s="10"/>
       <c r="R42" s="10"/>
@@ -2786,10 +2810,10 @@
     </row>
     <row r="43" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A43" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>18</v>
@@ -2823,9 +2847,11 @@
         <v>11</v>
       </c>
       <c r="N43" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O43" s="9"/>
+        <v>3</v>
+      </c>
+      <c r="O43" s="6" t="s">
+        <v>100</v>
+      </c>
       <c r="P43" s="10"/>
       <c r="Q43" s="10"/>
       <c r="R43" s="10"/>
@@ -2833,10 +2859,10 @@
     </row>
     <row r="44" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A44" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>2</v>
@@ -2875,7 +2901,7 @@
         <v>3</v>
       </c>
       <c r="O44" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P44" s="10"/>
       <c r="Q44" s="10"/>
@@ -2884,7 +2910,7 @@
     </row>
     <row r="45" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A45" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>1</v>
@@ -2926,7 +2952,7 @@
         <v>3</v>
       </c>
       <c r="O45" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P45" s="10"/>
       <c r="Q45" s="10"/>
@@ -2935,7 +2961,7 @@
     </row>
     <row r="46" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A46" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>1</v>
@@ -2977,7 +3003,7 @@
         <v>3</v>
       </c>
       <c r="O46" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P46" s="10"/>
       <c r="Q46" s="10"/>
@@ -2986,7 +3012,7 @@
     </row>
     <row r="47" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A47" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>1</v>
@@ -3028,7 +3054,7 @@
         <v>3</v>
       </c>
       <c r="O47" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P47" s="10"/>
       <c r="Q47" s="10"/>
@@ -3037,7 +3063,7 @@
     </row>
     <row r="48" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A48" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>1</v>
@@ -3089,7 +3115,7 @@
         <v>15</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>18</v>
@@ -3126,7 +3152,7 @@
         <v>3</v>
       </c>
       <c r="O49" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P49" s="10"/>
       <c r="Q49" s="10"/>
@@ -3135,10 +3161,10 @@
     </row>
     <row r="50" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A50" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>18</v>
@@ -3182,10 +3208,10 @@
     </row>
     <row r="51" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A51" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>18</v>
@@ -3232,7 +3258,7 @@
         <v>27</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>18</v>
@@ -3276,10 +3302,10 @@
     </row>
     <row r="53" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A53" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>18</v>
@@ -3323,10 +3349,10 @@
     </row>
     <row r="54" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A54" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>18</v>
@@ -3347,7 +3373,7 @@
         <v>0.5</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J54" s="6" t="s">
         <v>13</v>
@@ -3363,7 +3389,7 @@
         <v>3</v>
       </c>
       <c r="O54" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P54" s="10"/>
       <c r="Q54" s="10"/>
@@ -3372,10 +3398,10 @@
     </row>
     <row r="55" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A55" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>18</v>
@@ -3396,7 +3422,7 @@
         <v>0.5</v>
       </c>
       <c r="I55" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J55" s="6" t="s">
         <v>13</v>
@@ -3412,7 +3438,7 @@
         <v>3</v>
       </c>
       <c r="O55" s="14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P55" s="10"/>
       <c r="Q55" s="10"/>
@@ -3421,10 +3447,10 @@
     </row>
     <row r="56" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A56" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>18</v>
@@ -3468,22 +3494,22 @@
     </row>
     <row r="57" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A57" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E57" s="6" t="s">
         <v>13</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G57" s="15">
         <v>0.04</v>
@@ -3492,7 +3518,7 @@
         <v>0.5</v>
       </c>
       <c r="I57" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J57" s="6" t="s">
         <v>13</v>
@@ -3502,13 +3528,13 @@
       </c>
       <c r="L57" s="6"/>
       <c r="M57" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N57" s="14" t="s">
         <v>3</v>
       </c>
       <c r="O57" s="14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P57" s="10"/>
       <c r="Q57" s="10"/>
@@ -3517,10 +3543,10 @@
     </row>
     <row r="58" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A58" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>18</v>
@@ -3541,7 +3567,7 @@
         <v>0.5</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J58" s="6" t="s">
         <v>13</v>
@@ -3557,7 +3583,7 @@
         <v>3</v>
       </c>
       <c r="O58" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P58" s="10"/>
       <c r="Q58" s="10"/>
@@ -3566,10 +3592,10 @@
     </row>
     <row r="59" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A59" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>18</v>
@@ -3613,10 +3639,10 @@
     </row>
     <row r="60" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A60" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>18</v>
@@ -3653,7 +3679,7 @@
         <v>3</v>
       </c>
       <c r="O60" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P60" s="10"/>
       <c r="Q60" s="10"/>
@@ -3662,10 +3688,10 @@
     </row>
     <row r="61" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A61" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>18</v>
@@ -3709,10 +3735,10 @@
     </row>
     <row r="62" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A62" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>18</v>
@@ -3733,7 +3759,7 @@
         <v>0.5</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J62" s="12">
         <v>0</v>
@@ -3749,7 +3775,7 @@
         <v>3</v>
       </c>
       <c r="O62" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P62" s="5"/>
       <c r="Q62" s="5"/>
@@ -3758,10 +3784,10 @@
     </row>
     <row r="63" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A63" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>18</v>
@@ -3805,10 +3831,10 @@
     </row>
     <row r="64" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A64" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>18</v>
@@ -3829,7 +3855,7 @@
         <v>0.5</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J64" s="12">
         <v>0</v>
@@ -3855,7 +3881,7 @@
         <v>21</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>18</v>
@@ -3899,10 +3925,10 @@
     </row>
     <row r="66" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A66" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>18</v>
@@ -3949,7 +3975,7 @@
         <v>23</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>18</v>
@@ -3996,7 +4022,7 @@
         <v>17</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>18</v>
@@ -4033,7 +4059,7 @@
         <v>3</v>
       </c>
       <c r="O68" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P68" s="5"/>
       <c r="Q68" s="5"/>
@@ -4045,7 +4071,7 @@
         <v>20</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>18</v>
@@ -4082,7 +4108,7 @@
         <v>3</v>
       </c>
       <c r="O69" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P69" s="5"/>
       <c r="Q69" s="5"/>
@@ -4091,10 +4117,10 @@
     </row>
     <row r="70" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A70" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>18</v>
@@ -4131,7 +4157,7 @@
         <v>3</v>
       </c>
       <c r="O70" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P70" s="5"/>
       <c r="Q70" s="5"/>
@@ -4140,10 +4166,10 @@
     </row>
     <row r="71" spans="1:19" ht="15" x14ac:dyDescent="0.15">
       <c r="A71" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>18</v>
@@ -4180,7 +4206,7 @@
         <v>3</v>
       </c>
       <c r="O71" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P71" s="5"/>
       <c r="Q71" s="5"/>
@@ -4189,10 +4215,10 @@
     </row>
     <row r="72" spans="1:19" ht="16" x14ac:dyDescent="0.15">
       <c r="A72" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>18</v>
